--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/baseline_nested_confusion_22combined.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/baseline_nested_confusion_22combined.xlsx
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -568,13 +568,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -611,22 +611,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -638,14 +638,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>76% (n=29)</t>
+          <t>100% (n=13)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>56% (n=9)</t>
+          <t>79% (n=14)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -721,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -742,14 +742,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>67% (n=9)</t>
+          <t>86% (n=7)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>100% (n=3)</t>
+          <t>62% (n=8)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>

--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/baseline_nested_confusion_22combined.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/baseline_nested_confusion_22combined.xlsx
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -568,13 +568,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -611,22 +611,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -638,14 +638,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100% (n=13)</t>
+          <t>89% (n=27)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>79% (n=14)</t>
+          <t>57% (n=21)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -663,22 +663,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -721,10 +721,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -742,14 +742,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>86% (n=7)</t>
+          <t>100% (n=6)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>62% (n=8)</t>
+          <t>60% (n=5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>

--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/baseline_nested_confusion_22combined.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/baseline_nested_confusion_22combined.xlsx
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -620,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -638,14 +638,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>89% (n=27)</t>
+          <t>94% (n=16)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>57% (n=21)</t>
+          <t>33% (n=9)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -742,14 +742,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>100% (n=6)</t>
+          <t>100% (n=10)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60% (n=5)</t>
+          <t>41% (n=17)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>

--- a/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/baseline_nested_confusion_22combined.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelS_XSupport/tables/baseline_nested_confusion_22combined.xlsx
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>15</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -638,14 +638,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>94% (n=16)</t>
+          <t>94% (n=17)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33% (n=9)</t>
+          <t>65% (n=23)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>41% (n=17)</t>
+          <t>44% (n=9)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
